--- a/backtest_runs/20260410_193731/by_symbol/KHTC/KHTC.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/KHTC/KHTC.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-2384.759999999982</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>97615.24000000002</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>97615.24000000002</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>105858.37</v>
@@ -955,7 +955,7 @@
         <v>-664.0200000000049</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>105194.35</v>
@@ -1047,7 +1047,7 @@
         <v>-567.6300000000114</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>105297.88</v>
@@ -1185,7 +1185,7 @@
         <v>-42.83999999998133</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>108757.21</v>
@@ -1277,7 +1277,7 @@
         <v>-2641.799999999992</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>106243.93</v>
@@ -1415,7 +1415,7 @@
         <v>-2663.220000000013</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>105201.49</v>
@@ -1461,7 +1461,7 @@
         <v>-2527.559999999994</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>102673.93</v>
@@ -1645,7 +1645,7 @@
         <v>-1367.309999999994</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>110970.61</v>
